--- a/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/09_programs_initiatives.xlsx
+++ b/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/09_programs_initiatives.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rd4d656766ecd46c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R2201b30adbb64783"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R4715eea9ee524270"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="Rc9e4de468ff646ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R4756570c1516483d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R3e63c1e201464f1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R725b0a0fda6e4357"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R307a887ab0b748e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R169f2f6db8ca460a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R8c8efdceb924449f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R7ef50f237455466d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R1a1c6eb7781646b8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -628,7 +628,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9de2dbb9b624aab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90d6884847d048e2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -809,7 +809,7 @@
         <x:v>Executive Office cycle time; Executive Office quality and exception rate; Executive Office adoption / utilization</x:v>
       </x:c>
       <x:c r="O6" s="78" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Validate Enterprise profile and corporate priorities modernization and readiness program (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for programs initiatives.</x:v>
       </x:c>
       <x:c r="P6" s="41" t="str">
         <x:v>Medium</x:v>
@@ -859,7 +859,7 @@
         <x:v>Retail Deposits and Branch Operations cycle time; Retail Deposits and Branch Operations quality and exception rate; Retail Deposits and Branch Operations adoption / utilization</x:v>
       </x:c>
       <x:c r="O7" s="79" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Confirm Retail banking modernization and readiness program (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this programs initiatives record is used downstream.</x:v>
       </x:c>
       <x:c r="P7" s="45" t="str">
         <x:v>High</x:v>
@@ -909,7 +909,7 @@
         <x:v>Commercial Lending and Treasury cycle time; Commercial Lending and Treasury quality and exception rate; Commercial Lending and Treasury adoption / utilization</x:v>
       </x:c>
       <x:c r="O8" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Attach client evidence for Commercial banking modernization and readiness program (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P8" t="str">
         <x:v>High</x:v>
@@ -959,7 +959,7 @@
         <x:v>Cards Operations cycle time; Cards Operations quality and exception rate; Cards Operations adoption / utilization</x:v>
       </x:c>
       <x:c r="O9" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Reconcile Cards modernization and readiness program (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P9" t="str">
         <x:v>High</x:v>
@@ -1009,7 +1009,7 @@
         <x:v>Payments Operations cycle time; Payments Operations quality and exception rate; Payments Operations adoption / utilization</x:v>
       </x:c>
       <x:c r="O10" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Payments modernization and readiness program (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P10" t="str">
         <x:v>High</x:v>
@@ -1059,7 +1059,7 @@
         <x:v>Consumer Lending Operations cycle time; Consumer Lending Operations quality and exception rate; Consumer Lending Operations adoption / utilization</x:v>
       </x:c>
       <x:c r="O11" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Validate Lending modernization and readiness program (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for programs initiatives.</x:v>
       </x:c>
       <x:c r="P11" t="str">
         <x:v>Medium</x:v>
@@ -1109,7 +1109,7 @@
         <x:v>Wealth Advisory and Brokerage cycle time; Wealth Advisory and Brokerage quality and exception rate; Wealth Advisory and Brokerage adoption / utilization</x:v>
       </x:c>
       <x:c r="O12" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Confirm Wealth modernization and readiness program (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this programs initiatives record is used downstream.</x:v>
       </x:c>
       <x:c r="P12" t="str">
         <x:v>High</x:v>
@@ -1159,7 +1159,7 @@
         <x:v>Fraud and Risk Operations cycle time; Fraud and Risk Operations quality and exception rate; Fraud and Risk Operations adoption / utilization</x:v>
       </x:c>
       <x:c r="O13" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Validate Fraud / risk modernization and readiness program (record 8) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P13" t="str">
         <x:v>High</x:v>
@@ -1209,7 +1209,7 @@
         <x:v>Compliance and Model Risk Management cycle time; Compliance and Model Risk Management quality and exception rate; Compliance and Model Risk Management adoption / utilization</x:v>
       </x:c>
       <x:c r="O14" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Reconcile Compliance / model risk modernization and readiness program (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P14" t="str">
         <x:v>High</x:v>
@@ -1259,7 +1259,7 @@
         <x:v>Contact Center and Servicing cycle time; Contact Center and Servicing quality and exception rate; Contact Center and Servicing adoption / utilization</x:v>
       </x:c>
       <x:c r="O15" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Contact center modernization and readiness program (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P15" t="str">
         <x:v>High</x:v>
@@ -1309,7 +1309,7 @@
         <x:v>Digital Account Opening and Onboarding cycle time; Digital Account Opening and Onboarding quality and exception rate; Digital Account Opening and Onboarding adoption / utilization</x:v>
       </x:c>
       <x:c r="O16" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Validate Digital onboarding modernization and readiness program (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for programs initiatives.</x:v>
       </x:c>
       <x:c r="P16" t="str">
         <x:v>Medium</x:v>
@@ -1359,7 +1359,7 @@
         <x:v>Core Banking Modernization cycle time; Core Banking Modernization quality and exception rate; Core Banking Modernization adoption / utilization</x:v>
       </x:c>
       <x:c r="O17" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Confirm Core banking modernization modernization and readiness program (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this programs initiatives record is used downstream.</x:v>
       </x:c>
       <x:c r="P17" t="str">
         <x:v>High</x:v>
@@ -1409,7 +1409,7 @@
         <x:v>Customer 360 Data Product cycle time; Customer 360 Data Product quality and exception rate; Customer 360 Data Product adoption / utilization</x:v>
       </x:c>
       <x:c r="O18" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Attach client evidence for Customer 360 modernization and readiness program (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P18" t="str">
         <x:v>High</x:v>
@@ -1459,7 +1459,7 @@
         <x:v>Retail Banking Analytics cycle time; Retail Banking Analytics quality and exception rate; Retail Banking Analytics adoption / utilization</x:v>
       </x:c>
       <x:c r="O19" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Reconcile Retail banking analytics modernization and readiness program (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P19" t="str">
         <x:v>High</x:v>
@@ -1509,7 +1509,7 @@
         <x:v>Cards Portfolio Analytics cycle time; Cards Portfolio Analytics quality and exception rate; Cards Portfolio Analytics adoption / utilization</x:v>
       </x:c>
       <x:c r="O20" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cards analytics modernization and readiness program (record 15) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P20" t="str">
         <x:v>High</x:v>
@@ -1559,7 +1559,7 @@
         <x:v>Payments and Settlement Analytics cycle time; Payments and Settlement Analytics quality and exception rate; Payments and Settlement Analytics adoption / utilization</x:v>
       </x:c>
       <x:c r="O21" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Validate Payments analytics modernization and readiness program (record 16) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for programs initiatives.</x:v>
       </x:c>
       <x:c r="P21" t="str">
         <x:v>Medium</x:v>
@@ -1609,7 +1609,7 @@
         <x:v>Fraud and Risk Analytics cycle time; Fraud and Risk Analytics quality and exception rate; Fraud and Risk Analytics adoption / utilization</x:v>
       </x:c>
       <x:c r="O22" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Validate Fraud/risk analytics modernization and readiness program (record 17) against Fraud Analyst Copilot evidence: model version lineage gaps; confirm feature-store feedback loop owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P22" t="str">
         <x:v>High</x:v>
@@ -1659,7 +1659,7 @@
         <x:v>Cloud Data Platform cycle time; Cloud Data Platform quality and exception rate; Cloud Data Platform adoption / utilization</x:v>
       </x:c>
       <x:c r="O23" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Attach client evidence for Enterprise data platform / cloud data foundation modernization and readiness program (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P23" t="str">
         <x:v>High</x:v>
@@ -1709,7 +1709,7 @@
         <x:v>IT Budget and Tower Baseline cycle time; IT Budget and Tower Baseline quality and exception rate; IT Budget and Tower Baseline adoption / utilization</x:v>
       </x:c>
       <x:c r="O24" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Reconcile IT budget and Tower spend baseline modernization and readiness program (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P24" t="str">
         <x:v>High</x:v>
@@ -1759,7 +1759,7 @@
         <x:v>Vendor and Contract Optimization cycle time; Vendor and Contract Optimization quality and exception rate; Vendor and Contract Optimization adoption / utilization</x:v>
       </x:c>
       <x:c r="O25" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Vendor / contract / sourcing context modernization and readiness program (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P25" t="str">
         <x:v>High</x:v>
@@ -1809,7 +1809,7 @@
         <x:v>Infrastructure and CMDB cycle time; Infrastructure and CMDB quality and exception rate; Infrastructure and CMDB adoption / utilization</x:v>
       </x:c>
       <x:c r="O26" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Validate CMDB / infrastructure / cloud inventory context modernization and readiness program (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for programs initiatives.</x:v>
       </x:c>
       <x:c r="P26" t="str">
         <x:v>Medium</x:v>
@@ -1859,7 +1859,7 @@
         <x:v>Incident Problem Change Operations cycle time; Incident Problem Change Operations quality and exception rate; Incident Problem Change Operations adoption / utilization</x:v>
       </x:c>
       <x:c r="O27" t="str">
-        <x:v>Need approved charter, baseline, funding, owner attestation, and phase gate evidence.</x:v>
+        <x:v>Confirm Incident / problem / change operational health context modernization and readiness program (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this programs initiatives record is used downstream.</x:v>
       </x:c>
       <x:c r="P27" t="str">
         <x:v>High</x:v>
@@ -1880,7 +1880,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3729251cd4bf4ec9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re71364c558624dfb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1955,7 +1955,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29fc128694d14e8d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8993d27adc3146b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2149,7 +2149,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bb06e720b25456e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc1cfa95340344b64"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2211,7 +2211,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2dd156c8be484d73"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38f029359df54d41"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2321,7 +2321,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49fd38af30684085"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2bbf56c102741a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>